--- a/self_dataset/compare_results/unchecked-send.xlsx
+++ b/self_dataset/compare_results/unchecked-send.xlsx
@@ -420,13 +420,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>buggy_1_HotDollarsToken.txt</t>
+          <t>buggy_11_ForTheBlockchain.txt</t>
         </is>
       </c>
     </row>
@@ -460,10 +460,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -471,76 +471,76 @@
         <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>buggy_2_CareerOnToken.txt</t>
-        </is>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>buggy_11_Owned.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>105</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>buggy_3_CareerOnToken.txt</t>
+          <t>buggy_12_ERC223Token.txt</t>
         </is>
       </c>
     </row>
@@ -571,99 +571,99 @@
         <v>105</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>110</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>buggy_12_Grand.txt</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>buggy_4_PHO.txt</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>105</v>
-      </c>
-      <c r="B18" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-2</v>
+      <c r="A17" t="n">
+        <v>105</v>
+      </c>
+      <c r="B17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_ERC20.txt</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>buggy_6_ChannelWallet.txt</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A21" t="n">
+        <v>101</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -671,19 +671,19 @@
         <v>105</v>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>buggy_7_AccountWallet.txt</t>
+          <t>buggy_14_SaveWon.txt</t>
         </is>
       </c>
     </row>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -728,19 +728,19 @@
         <v>105</v>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>buggy_9_XLToken.txt</t>
+          <t>buggy_16_ExclusivePlatform.txt</t>
         </is>
       </c>
     </row>
@@ -771,13 +771,13 @@
         <v>101</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -785,38 +785,732 @@
         <v>105</v>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>107</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>113</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>buggy_17_AZT.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>101</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>105</v>
+      </c>
+      <c r="B39" t="n">
+        <v>30</v>
+      </c>
+      <c r="C39" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>110</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>116</v>
+      </c>
+      <c r="B41" t="n">
         <v>2</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C41" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18__Yesbuzz.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>101</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>105</v>
+      </c>
+      <c r="B46" t="n">
+        <v>31</v>
+      </c>
+      <c r="C46" t="n">
+        <v>31</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>107</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>buggy_19_ethBank.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>101</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105</v>
+      </c>
+      <c r="B52" t="n">
+        <v>28</v>
+      </c>
+      <c r="C52" t="n">
+        <v>28</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>buggy_1_HotDollarsToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>101</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>105</v>
+      </c>
+      <c r="B57" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" t="n">
+        <v>18</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>buggy_20_Stoppable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>105</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>buggy_2_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>105</v>
+      </c>
+      <c r="B65" t="n">
+        <v>13</v>
+      </c>
+      <c r="C65" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>110</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>buggy_3_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>105</v>
+      </c>
+      <c r="B70" t="n">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>21</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>110</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>buggy_4_PHO.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>101</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105</v>
+      </c>
+      <c r="B76" t="n">
+        <v>18</v>
+      </c>
+      <c r="C76" t="n">
+        <v>18</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>buggy_6_ChannelWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>101</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>105</v>
+      </c>
+      <c r="B81" t="n">
+        <v>30</v>
+      </c>
+      <c r="C81" t="n">
+        <v>30</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>buggy_7_AccountWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>101</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>105</v>
+      </c>
+      <c r="B86" t="n">
+        <v>31</v>
+      </c>
+      <c r="C86" t="n">
+        <v>31</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>buggy_9_XLToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>101</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>105</v>
+      </c>
+      <c r="B91" t="n">
+        <v>24</v>
+      </c>
+      <c r="C91" t="n">
+        <v>24</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>110</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="18">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
